--- a/recipes/onion-garlic-free-indian/focus-states/02-maharashtra/excel/maharashtra-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/02-maharashtra/excel/maharashtra-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bharli Vangi (no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bharli Vangi (no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Side  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 15 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -1764,38 +1767,204 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Fill slits. Cook covered until soft and the masala clings.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Fill slits. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Cook covered until soft and the masala clings. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 277  ·  Protein 4 g  ·  Carbs 34 g  ·  Fat 15 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Bharli Vangi (no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="32">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1809,7 +1978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1821,7 +1990,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Farasbi Chi Bhaji</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Farasbi Chi Bhaji</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1831,7 +2000,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Side  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1851,44 +2020,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -2090,37 +2259,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Temper, stir-fry, coconut.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Temper, stir-fry, coconut. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 299  ·  Protein 14 g  ·  Carbs 42 g  ·  Fat 9 g  ·  Fibre 12 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Farasbi Chi Bhaji: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2134,7 +2469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2146,7 +2481,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Palak Bhaji</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Palak Bhaji</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2156,7 +2491,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Side  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2176,44 +2511,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -2397,36 +2732,215 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Wilt in a steel pan. No onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Wash greens in several changes of water; drain and squeeze dry.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Wilt in a steel pan. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>No onion. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 22  ·  Protein 2 g  ·  Carbs 4 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Wash greens until the water is clear; grit ruins the dish. For Palak Bhaji: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2440,7 +2954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2452,7 +2966,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Jowar Bhakri</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Jowar Bhakri</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2462,7 +2976,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Bread  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2482,44 +2996,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2649,33 +3163,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Pat, cook on iron, puff on flame.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Pat, cook on iron, puff on flame. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 72  ·  Protein 2 g  ·  Carbs 11 g  ·  Fat 2 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Jowar Bhakri: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2689,7 +3356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2701,7 +3368,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Wheat Poli</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Wheat Poli</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2711,7 +3378,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Bread  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2731,44 +3398,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2898,33 +3565,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Phulka-style on iron tawa.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Phulka-style on iron tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 318  ·  Protein 9 g  ·  Carbs 54 g  ·  Fat 8 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Wheat Poli: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2938,7 +3758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2950,7 +3770,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Puri</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Puri</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2960,7 +3780,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Bread  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2980,44 +3800,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -3165,34 +3985,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Roll small, fry in steel until they puff.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Roll small, fry in steel until they puff. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 380  ·  Protein 9 g  ·  Carbs 54 g  ·  Fat 15 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Puri: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3206,7 +4179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3218,7 +4191,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Ukadiche Modak</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Ukadiche Modak</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3228,7 +4201,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Sweet  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3248,44 +4221,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 30 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -3397,32 +4370,185 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="66" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Shape, steam 10 minutes in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Shape, steam 10 minutes in steel. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>kcal 447  ·  Protein 7 g  ·  Carbs 67 g  ·  Fat 17 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>For Ukadiche Modak: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="25">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3436,7 +4562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3448,7 +4574,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Puran Poli</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Puran Poli</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3458,7 +4584,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Sweet  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3478,44 +4604,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>65 min</t>
+          <t>Prep 40 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -3627,32 +4753,185 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Stuff, roll thin, cook on iron with ghee.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Stuff, roll thin, cook on iron with ghee. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>kcal 345  ·  Protein 14 g  ·  Carbs 69 g  ·  Fat 3 g  ·  Fibre 12 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>For Puran Poli: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="25">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3666,7 +4945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3678,7 +4957,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chirote</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chirote</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3688,7 +4967,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Sweet  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3708,44 +4987,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 25 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -3911,35 +5190,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Layer with ghee, roll, cut, fry in steel, dust sugar.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Layer with ghee, roll, cut, fry in steel, dust sugar. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 450  ·  Protein 6 g  ·  Carbs 73 g  ·  Fat 15 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Chirote: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3953,7 +5385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3965,7 +5397,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Amrakhand</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Amrakhand</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3975,7 +5407,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Dessert  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3995,44 +5427,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -4180,34 +5612,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Whisk, chill.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Whisk, chill. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 195  ·  Protein 3 g  ·  Carbs 43 g  ·  Fat 2 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Amrakhand: keep it cold and set before service. Never store yogurt or milk sweets in aluminium. Garnish nuts only if the allergen card allows. Read spice and hing labels if used.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4485,7 +6070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4497,7 +6082,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kesar Shrikhand</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kesar Shrikhand</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4507,7 +6092,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Dessert  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4527,44 +6112,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -4730,35 +6315,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Whisk, chill.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Whisk, chill. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Chilled.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 156  ·  Protein 3 g  ·  Carbs 29 g  ·  Fat 4 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Kesar Shrikhand: keep it cold and set before service. Never store yogurt or milk sweets in aluminium. Garnish nuts only if the allergen card allows. Read spice and hing labels if used.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve in a steel or glass bowl. Stir at the pass so it is not split or settled. Service temperature: Chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4772,7 +6510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4784,7 +6522,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Basundi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Basundi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4794,7 +6532,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Dessert  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4814,44 +6552,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>Prep 10 min · Cook 45 min</t>
         </is>
       </c>
     </row>
@@ -5017,35 +6755,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Reduce in a heavy steel pot, scraping cream back in.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Reduce in a heavy steel pot, scraping cream back in. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 110  ·  Protein 0 g  ·  Carbs 27 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Basundi: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5059,7 +6950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5071,7 +6962,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kakdi Koshimbir</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kakdi Koshimbir</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5081,7 +6972,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Salad  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5101,44 +6992,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>Prep 8 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5340,37 +7231,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="54" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Mix. Peanut and lemon replace onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Mix. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Peanut and lemon replace onion. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 147  ·  Protein 3 g  ·  Carbs 9 g  ·  Fat 12 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Peanuts · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Kakdi Koshimbir: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Peanuts; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5384,7 +7441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5396,7 +7453,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Tomato Coconut Koshimbir</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Tomato Coconut Koshimbir</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5406,7 +7463,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Salad  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5426,44 +7483,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>Prep 8 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5647,36 +7704,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="54" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Toss.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 103  ·  Protein 1 g  ·  Carbs 7 g  ·  Fat 9 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Tomato Coconut Koshimbir: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5690,7 +7900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5702,7 +7912,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Dahi Koshimbir</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Dahi Koshimbir</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5712,7 +7922,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Salad  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5732,44 +7942,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>Prep 8 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5935,35 +8145,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Mix. Chill.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Mix. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Chill. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 49  ·  Protein 3 g  ·  Carbs 7 g  ·  Fat 2 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Dahi Koshimbir: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9229,7 +11605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9241,7 +11617,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kothimbir Vadi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kothimbir Vadi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9251,7 +11627,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Starter  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9271,44 +11647,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 20 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -9510,37 +11886,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Steam 12 minutes, slice, pan-fry in steel until crisp.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel steamer and steel thali — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="66" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Steam 12 minutes, slice, pan-fry in steel until crisp. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 243  ·  Protein 11 g  ·  Carbs 33 g  ·  Fat 8 g  ·  Fibre 6 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Kothimbir Vadi: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9554,7 +12096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9566,7 +12108,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sabudana Vada</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sabudana Vada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9576,7 +12118,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Starter  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9596,44 +12138,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -9835,37 +12377,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Shape, fry in a steel kadhai. Serve with coconut chutney (no garlic).</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Shape, fry in a steel kadhai. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Serve with coconut chutney (no garlic). Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 254  ·  Protein 4 g  ·  Carbs 9 g  ·  Fat 23 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Sabudana Vada: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9879,7 +12587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9891,7 +12599,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Thalipeeth Bites</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Thalipeeth Bites</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9901,7 +12609,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Starter  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9921,44 +12629,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -10142,36 +12850,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="54" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Pat small rounds on iron tawa. Cook both sides.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Pat small rounds on iron tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cook both sides. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 211  ·  Protein 5 g  ·  Carbs 23 g  ·  Fat 12 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Thalipeeth Bites: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10185,7 +13059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10197,7 +13071,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pithla</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pithla</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10207,7 +13081,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Main  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10227,44 +13101,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -10520,40 +13394,219 @@
       <c r="C25" s="46" t="n"/>
       <c r="D25" s="46" t="n"/>
     </row>
-    <row r="26" ht="42" customHeight="1">
+    <row r="26" ht="66" customHeight="1">
       <c r="A26" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B26" s="48" t="inlineStr">
         <is>
-          <t>Temper, pour besan slurry, cook until the raw smell goes. Serve with bhakri.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C26" s="49" t="n"/>
       <c r="D26" s="49" t="n"/>
     </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="66" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Temper, pour besan slurry, cook until the raw smell goes. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Serve with bhakri. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>kcal 126  ·  Protein 7 g  ·  Carbs 19 g  ·  Fat 2 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>For Pithla: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B41" s="52" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B42" s="50" t="n"/>
+      <c r="C42" s="50" t="n"/>
+      <c r="D42" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="35">
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10567,7 +13620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10579,7 +13632,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kokum Amti</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kokum Amti</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10589,7 +13642,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Main  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10609,44 +13662,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -10866,38 +13919,230 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="42" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Cook dal, add kokum and jaggery. Temper. Should taste sour-sweet, not garlicky.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Cook dal, add kokum and jaggery. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Temper. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Should taste sour-sweet, not garlicky. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>kcal 219  ·  Protein 7 g  ·  Carbs 46 g  ·  Fat 1 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>For Kokum Amti: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B40" s="52" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="52" t="n"/>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B41" s="50" t="n"/>
+      <c r="C41" s="50" t="n"/>
+      <c r="D41" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="34">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10911,7 +14156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10923,7 +14168,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Varan Bhaat</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Varan Bhaat</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10933,7 +14178,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Maharashtra kitchen  ·  Main  ·  Maharashtrian vegetarian and vrat cooking</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Maharashtra  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10953,44 +14198,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 10 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -11192,37 +14437,229 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Cook dal very soft. Tadka ghee, cumin, hing. Pour over hot rice with more ghee.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel or clay pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel or clay pot — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cook dal very soft. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Tadka ghee, cumin, hing. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Pour over hot rice with more ghee. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 522  ·  Protein 13 g  ·  Carbs 97 g  ·  Fat 8 g  ·  Fibre 6 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Varan Bhaat: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="33">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
